--- a/06_CRP.xlsx
+++ b/06_CRP.xlsx
@@ -1375,10 +1375,10 @@
         <v>100</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>80</v>
@@ -1420,22 +1420,22 @@
         <v>90</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="Y2" s="2" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="Z2" s="2" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AA2" s="2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AC2" s="2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AD2" s="2" t="n">
         <v>0</v>
